--- a/output/swarajability.xlsx
+++ b/output/swarajability.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -443,7 +443,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="43" customWidth="1" min="16" max="16"/>
+    <col width="49" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
   </cols>
@@ -543,12 +543,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BELL BOY</t>
+          <t>Machine Operator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotel</t>
+          <t>TATA Motors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -577,26 +577,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INR 150000 - 225000 per year</t>
+          <t>INR 175000 - 200000 per year</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>150000</v>
+        <v>175000</v>
       </c>
       <c r="M2" t="n">
-        <v>225000</v>
+        <v>200000</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8854</t>
+          <t>https://portal.swarajability.org/apply-job/8870</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,19 +606,19 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.Guiding customer 2.Customer supprt</t>
+          <t>Eligibility: Qualification- 12th Pass, ITI (all trades), graduates- any stream Minimum marks- 50%. Relaxed by 5% for PwD Age- 18 years to 25 years Disability category- SHI Those 12th pass (and graduates) will have 3 year duration and those with ITI have 2 years duration Monthly stipend will be 17K/m</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PACKER</t>
+          <t>Loaders and Unloaders</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pasuparthy's Super Market</t>
+          <t>Flipkart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -647,26 +647,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 200000 - 225000 per year</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="M3" t="n">
-        <v>150000</v>
+        <v>225000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8851</t>
+          <t>https://portal.swarajability.org/apply-job/8868</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>Sorting Packing Picking Loading &amp; Unloading</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRAINEE</t>
+          <t>Picker Packer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hero Moto Crop Limited</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -717,26 +717,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 225000 - 250000 per year</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>125000</v>
+        <v>225000</v>
       </c>
       <c r="M4" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8850</t>
+          <t>https://portal.swarajability.org/apply-job/8867</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -746,19 +746,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>HERO COMPANY</t>
+          <t>Sorting Picking Packing Scanning packages Loading/Unloading packages</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cashier/ Customer Service Executive</t>
+          <t>Production/Assembly Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chai Kings</t>
+          <t>Forbes Marshall</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -787,26 +787,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 250000 - 500000 per year</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>125000</v>
+        <v>250000</v>
       </c>
       <c r="M5" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8849</t>
+          <t>https://portal.swarajability.org/apply-job/8866</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -816,19 +816,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Qualification: BE Electronics with a Mechanical background. Job Profile: - Willingness to work in any assembly area as per demand. - Proficiency with ERP systems. - Managing assembly and preparation of mechanical parts. - Conducting electronics testing and maintaining detailed records. - Testing bou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Virtual RM-VRM</t>
+          <t>packing picking, Scanning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hdfc bank</t>
+          <t>2 COMS CONSULTING PVT LTD KOLKATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -857,26 +857,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INR 500000 - 800000 per year</t>
+          <t>INR 150000 - 200000 per year</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>500000</v>
+        <v>150000</v>
       </c>
       <c r="M6" t="n">
-        <v>800000</v>
+        <v>200000</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8845</t>
+          <t>https://portal.swarajability.org/apply-job/8865</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -886,19 +886,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Banking Job customer handling</t>
+          <t>packing picking, Scanning</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Packer</t>
+          <t>Customer Service Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARATM MULTISTATES</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -927,26 +927,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INR 50000 - 100000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>50000</v>
+        <v>125000</v>
       </c>
       <c r="M7" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8840</t>
+          <t>https://portal.swarajability.org/apply-job/8864</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -956,19 +956,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Any Person Can apply Rule Follow to Siriusly.</t>
+          <t>Customer Assistance: Welcoming shoppers, offering product knowledge, and assisting with product selection, sizing, or styling. Sales &amp; Promotion: Suggesting additional items (cross-selling/upselling) and informing customers about current promotions or loyalty programs. Checkout Operations: Processin</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stewards, service</t>
+          <t>Customer Service Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BARBEQUE NATION</t>
+          <t>Ushodaya Supermarket</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -997,26 +997,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INR 100000 - 125000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="M8" t="n">
-        <v>125000</v>
+        <v>150000</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8839</t>
+          <t>https://portal.swarajability.org/apply-job/8863</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Customer Assistance: Welcoming shoppers, offering product knowledge, and assisting with product selection, sizing, or styling. Sales &amp; Promotion: Suggesting additional items (cross-selling/upselling) and informing customers about current promotions or loyalty programs. Checkout Operations: Processin</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pickers &amp; Packers</t>
+          <t>Fashion Assistant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Big Basket</t>
+          <t>Style Union Boduppal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8833</t>
+          <t>https://portal.swarajability.org/apply-job/8861</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1096,19 +1096,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Picking &amp; Packing, scanning roles</t>
+          <t>Core Responsibilities— *Personalized Styling: Greet shoppers, assess their personal style or occasion needs, and pull together outfits, accessories, and footwear. *Sales &amp; Up-Selling: Promote new collections, cross-sell complementary items, and consistently meet or exceed individual and store sales</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stewards, service</t>
+          <t>pecking packing scanning</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barbeque Nation</t>
+          <t>Firstcry Pvt.Ltd (kolkata)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1137,26 +1137,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 150000 - 175000 per year</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>125000</v>
+        <v>150000</v>
       </c>
       <c r="M10" t="n">
-        <v>150000</v>
+        <v>175000</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8828</t>
+          <t>https://portal.swarajability.org/apply-job/8860</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1166,19 +1166,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Service/Stewards</t>
+          <t>pecking packing scanning</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Picking, packing, scanning,</t>
+          <t>packing Packing Scanning</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>A. B. ENTERPRISES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1207,26 +1207,26 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
+        <v>125000</v>
+      </c>
+      <c r="M11" t="n">
         <v>150000</v>
-      </c>
-      <c r="M11" t="n">
-        <v>175000</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8819</t>
+          <t>https://portal.swarajability.org/apply-job/8859</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Picking, packing, scanning,</t>
+          <t>packing Packing Scanning</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Picking, packing, scanning</t>
+          <t>Contract Associates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 COMS CONSULTING PVT LTD KOLKATA</t>
+          <t>Spark Minda</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1277,26 +1277,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 250000 - 275000 per year</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="M12" t="n">
-        <v>175000</v>
+        <v>275000</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8818</t>
+          <t>https://portal.swarajability.org/apply-job/8856</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1306,19 +1306,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Picking, packing, scanning</t>
+          <t>Minda Corporation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Picking, packing, scaning</t>
+          <t>Picker &amp; Packer, Delivery executive</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adhaan solution pvt.ltd (KOLKATA)</t>
+          <t>Pizza Hut</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1347,26 +1347,26 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M13" t="n">
         <v>150000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>175000</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8816</t>
+          <t>https://portal.swarajability.org/apply-job/8855</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1376,19 +1376,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Picking, packing, scanning</t>
+          <t>Picking &amp; Packing, Delivering ordered products to the location</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>BELL BOY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mitti Social Initiatives Foundation</t>
+          <t>Lemon Tree Hotel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1431,12 +1431,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8813</t>
+          <t>https://portal.swarajability.org/apply-job/8854</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1446,19 +1446,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Billing. Cash Handling. Customer Service. *Rotational Shift. Contact-9281147013.</t>
+          <t>1.Guiding customer 2.Customer supprt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Cashier/ Customer Service Executive</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zepto -Puducherry</t>
+          <t>Chai Kings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1501,12 +1501,12 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8800</t>
+          <t>https://portal.swarajability.org/apply-job/8849</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1516,19 +1516,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Delivery jobs</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Virtual RM-VRM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zepto -Puducherry</t>
+          <t>Hdfc bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1557,26 +1557,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 500000 - 800000 per year</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="M16" t="n">
-        <v>150000</v>
+        <v>800000</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8799</t>
+          <t>https://portal.swarajability.org/apply-job/8845</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1586,19 +1586,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Delivery jobs</t>
+          <t>Banking Job customer handling</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Packer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zepto -Puducherry</t>
+          <t>BHARATM MULTISTATES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1627,26 +1627,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 50000 - 100000 per year</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>125000</v>
+        <v>50000</v>
       </c>
       <c r="M17" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8798</t>
+          <t>https://portal.swarajability.org/apply-job/8840</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1656,19 +1656,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Delivery jobs</t>
+          <t>Any Person Can apply Rule Follow to Siriusly.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Stewards, service</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zepto -Puducherry</t>
+          <t>BARBEQUE NATION</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1697,26 +1697,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 100000 - 125000 per year</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M18" t="n">
         <v>125000</v>
-      </c>
-      <c r="M18" t="n">
-        <v>150000</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8797</t>
+          <t>https://portal.swarajability.org/apply-job/8839</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1726,19 +1726,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Delivery jobs</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Customer service executive</t>
+          <t>Pickers &amp; Packers</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zudio</t>
+          <t>Big Basket</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1781,12 +1781,12 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8792</t>
+          <t>https://portal.swarajability.org/apply-job/8833</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1796,19 +1796,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Customer Support service</t>
+          <t>Picking &amp; Packing, scanning roles</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apprentice Trainee</t>
+          <t>Stewards, service</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Westside Chennai</t>
+          <t>Barbeque Nation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1851,12 +1851,12 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8791</t>
+          <t>https://portal.swarajability.org/apply-job/8828</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Upon successful completion of the Apprentice role, candidates will be converted to On-Roll employees with the following details: On-Roll Employment Details: - Customer Service Associate - Designation - Sales Associate - Salary: ₹16900 Gross Per month + Incentives - Benefits: ESI,PF, Gratuity etc. Jo</t>
+          <t>Service/Stewards</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Quality Checker and Production Operator</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anusham Automotive India Private Limited</t>
+          <t>Zepto -Puducherry</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1907,26 +1907,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INR 200000 - 225000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>200000</v>
+        <v>125000</v>
       </c>
       <c r="M21" t="n">
-        <v>225000</v>
+        <v>150000</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8787</t>
+          <t>https://portal.swarajability.org/apply-job/8800</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1936,19 +1936,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Quality Checker Check finished products for defects or damages Measure product size, weight, and specifications Maintain quality records and reports Identify rejected materials and inform supervisor Follow company quality procedures Keep work area clean and safe Production Operator Operate productio</t>
+          <t>Delivery jobs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Digital Customer Specialist</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cropone Global Solutions Pvt Ltd</t>
+          <t>Zepto -Puducherry</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1977,26 +1977,26 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INR 175000 - 200000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>175000</v>
+        <v>125000</v>
       </c>
       <c r="M22" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8779</t>
+          <t>https://portal.swarajability.org/apply-job/8799</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2006,19 +2006,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Job Responsibilities: * Handle customer queries through calls/digital channels * Follow up with customers for loan collections and payment reminders * Provide payment details and support to customers * Maintain professional communication with customers * Update customer interaction details in the sy</t>
+          <t>Delivery jobs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>captain</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Zepto -Puducherry</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -2047,26 +2047,26 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INR 175000 - 200000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>175000</v>
+        <v>125000</v>
       </c>
       <c r="M23" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8757</t>
+          <t>https://portal.swarajability.org/apply-job/8798</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>picker</t>
+          <t>Delivery jobs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calling Associate</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jaagruk Bharat</t>
+          <t>Zepto -Puducherry</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>100000</v>
+        <v>125000</v>
       </c>
       <c r="M24" t="n">
         <v>150000</v>
@@ -2131,12 +2131,12 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8752</t>
+          <t>https://portal.swarajability.org/apply-job/8797</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2146,19 +2146,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Work From Home with 12000 Salary</t>
+          <t>Delivery jobs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GIS Analyst</t>
+          <t>Apprentice Trainee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAPe IT Solution</t>
+          <t>Westside Chennai</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2187,26 +2187,26 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INR 150000 - 300000 per year</t>
+          <t>INR 125000 - 150000 per year</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
+        <v>125000</v>
+      </c>
+      <c r="M25" t="n">
         <v>150000</v>
-      </c>
-      <c r="M25" t="n">
-        <v>300000</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8743</t>
+          <t>https://portal.swarajability.org/apply-job/8791</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2216,19 +2216,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Perform assigned duties efficiently and on time.</t>
+          <t>Upon successful completion of the Apprentice role, candidates will be converted to On-Roll employees with the following details: On-Roll Employment Details: - Customer Service Associate - Designation - Sales Associate - Salary: ₹16900 Gross Per month + Incentives - Benefits: ESI,PF, Gratuity etc. Jo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Quality Checker and Production Operator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NIKASH CNC ENGINEERS PVT LTD</t>
+          <t>Anusham Automotive India Private Limited</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -2257,13 +2257,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INR 150000 - 225000 per year</t>
+          <t>INR 200000 - 225000 per year</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="M26" t="n">
         <v>225000</v>
@@ -2271,12 +2271,12 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8742</t>
+          <t>https://portal.swarajability.org/apply-job/8787</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2286,19 +2286,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Packaging, Stickering</t>
+          <t>Quality Checker Check finished products for defects or damages Measure product size, weight, and specifications Maintain quality records and reports Identify rejected materials and inform supervisor Follow company quality procedures Keep work area clean and safe Production Operator Operate productio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Telemarketing</t>
+          <t>Digital Customer Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indira Enterprices</t>
+          <t>Cropone Global Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2327,26 +2327,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INR 100000 - 300000 per year</t>
+          <t>INR 175000 - 200000 per year</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>100000</v>
+        <v>175000</v>
       </c>
       <c r="M27" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8740</t>
+          <t>https://portal.swarajability.org/apply-job/8779</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Perform assigned duties efficiently and on time.</t>
+          <t>Job Responsibilities: * Handle customer queries through calls/digital channels * Follow up with customers for loan collections and payment reminders * Provide payment details and support to customers * Maintain professional communication with customers * Update customer interaction details in the sy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Operator</t>
+          <t>Calling Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vimoni India Pvt Ltd</t>
+          <t>Jaagruk Bharat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2397,26 +2397,26 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M28" t="n">
         <v>150000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>175000</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8735</t>
+          <t>https://portal.swarajability.org/apply-job/8752</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Machine Operator</t>
+          <t>Work From Home with 12000 Salary</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Picking and packing</t>
+          <t>GIS Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KVB Staffing Solutions Private Limited</t>
+          <t>MAPe IT Solution</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2467,16 +2467,16 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 150000 - 300000 per year</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>125000</v>
+        <v>150000</v>
       </c>
       <c r="M29" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8733</t>
+          <t>https://portal.swarajability.org/apply-job/8743</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2496,19 +2496,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Picking Paking</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Picker Packer</t>
+          <t>Helper</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bigbasket</t>
+          <t>NIKASH CNC ENGINEERS PVT LTD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 150000 - 225000 per year</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -2546,7 +2546,7 @@
         <v>150000</v>
       </c>
       <c r="M30" t="n">
-        <v>175000</v>
+        <v>225000</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8732</t>
+          <t>https://portal.swarajability.org/apply-job/8742</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Picker and Packer role</t>
+          <t>Packaging, Stickering</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Operator</t>
+          <t>Telemarketing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Genius consultants ltd</t>
+          <t>Indira Enterprices</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2607,26 +2607,26 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INR 125000 - 200000 per year</t>
+          <t>INR 100000 - 300000 per year</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="M31" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8731</t>
+          <t>https://portal.swarajability.org/apply-job/8740</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2636,19 +2636,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Food Service in Company cafetaria</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vishual Inspection</t>
+          <t>Operator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amneal Pharmaceuticals pvt ltd</t>
+          <t>Genius consultants ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2677,16 +2677,16 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INR 200000 - 325000 per year</t>
+          <t>INR 125000 - 200000 per year</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
+        <v>125000</v>
+      </c>
+      <c r="M32" t="n">
         <v>200000</v>
-      </c>
-      <c r="M32" t="n">
-        <v>325000</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8730</t>
+          <t>https://portal.swarajability.org/apply-job/8731</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Inspection of the injection</t>
+          <t>Food Service in Company cafetaria</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tailoring</t>
+          <t>Vishual Inspection</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zwilling foundation india</t>
+          <t>Amneal Pharmaceuticals pvt ltd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2747,16 +2747,16 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 200000 - 325000 per year</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="M33" t="n">
-        <v>150000</v>
+        <v>325000</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8729</t>
+          <t>https://portal.swarajability.org/apply-job/8730</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2776,19 +2776,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Tailoring and quality checking</t>
+          <t>Inspection of the injection</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Customer Service Champion</t>
+          <t>Kitchen Helper, Brew Master</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shell Petrol Pump</t>
+          <t>Bon Fresh Foods pvt ltd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2817,16 +2817,16 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INR 175000 - 250000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>175000</v>
+        <v>100000</v>
       </c>
       <c r="M34" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8726</t>
+          <t>https://portal.swarajability.org/apply-job/8722</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2846,19 +2846,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Customer Handle</t>
+          <t>1. Job Description · Tea and Coffee making. Ready to learn the process. · Preparing quick meals like Magi, Poha, Bread Butter Jam etc. · Following Grooming Standards · Cleaning the tea making utensils · Mopping and cleaning the floor and ensuring the store is hygienically maintained · Cleaning table</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kitchen Helper, Brew Master</t>
+          <t>Flexi Barista</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bon Fresh Foods pvt ltd</t>
+          <t>Tata Starbucks Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2887,26 +2887,26 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 200000 - 225000 per year</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="M35" t="n">
-        <v>150000</v>
+        <v>225000</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8722</t>
+          <t>https://portal.swarajability.org/apply-job/8703</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2916,19 +2916,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1. Job Description · Tea and Coffee making. Ready to learn the process. · Preparing quick meals like Magi, Poha, Bread Butter Jam etc. · Following Grooming Standards · Cleaning the tea making utensils · Mopping and cleaning the floor and ensuring the store is hygienically maintained · Cleaning table</t>
+          <t>Baristas are the face of Starbucks. They are an important part of our customers’ days, and experts in handcrafting delicious, perfect beverages. Baristas personally connect and create moments that make a difference. They are the heroes who bring our values and mission to life everyday - not wearing</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Flexi Barista</t>
+          <t>Customer Sales Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Starbucks Pvt. Ltd.</t>
+          <t>KPN FARM FRESH PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INR 200000 - 225000 per year</t>
+          <t>INR 200000 - 250000 per year</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2966,17 +2966,17 @@
         <v>200000</v>
       </c>
       <c r="M36" t="n">
-        <v>225000</v>
+        <v>250000</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8703</t>
+          <t>https://portal.swarajability.org/apply-job/8662</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2986,19 +2986,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Baristas are the face of Starbucks. They are an important part of our customers’ days, and experts in handcrafting delicious, perfect beverages. Baristas personally connect and create moments that make a difference. They are the heroes who bring our values and mission to life everyday - not wearing</t>
+          <t>• Arrange and organize products neatly on shelves and storage areas • Pick and pack items accurately for online orders • Assist in stock handling, replenishment, and inventory checks • Check product quality, expiry dates, and proper labelling • Maintain cleanliness in the work area</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vimoni India Pvt Ltd</t>
+          <t>Zudio - AP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -3027,13 +3027,13 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INR 125000 - 150000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="M37" t="n">
         <v>150000</v>
@@ -3041,12 +3041,12 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8697</t>
+          <t>https://portal.swarajability.org/apply-job/8650</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3056,19 +3056,19 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Bottle Making companny</t>
+          <t>Visual Merchandiser : Arranges products, displays, and signage to attract customers and promote sales</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Customer Service Executive</t>
+          <t>Kitchen Staff</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Bon Fresh Foods pvt ltd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -3097,26 +3097,26 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INR 175000 - 200000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>175000</v>
+        <v>100000</v>
       </c>
       <c r="M38" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8685</t>
+          <t>https://portal.swarajability.org/apply-job/8580</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3126,19 +3126,19 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Roles: Customer service, Stewards, House Keeping Office Boys</t>
+          <t>· Preparing quick meals like Magi, Poha, Bread Butter Jam etc. · Following Grooming Standards · Cleaning the tea making utensils · Mopping and cleaning the floor and ensuring the store is hygienically maintained · Cleaning tables and chairs · Reporting to duty on time as per the shift schedule · Mak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Customer Sales Associate</t>
+          <t>Sr Equity Dealer / Equity Dealer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KPN FARM FRESH PRIVATE LIMITED</t>
+          <t>Axis Securities Limited</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -3165,28 +3165,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>INR 200000 - 250000 per year</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
-        <v>200000</v>
-      </c>
-      <c r="M39" t="n">
-        <v>250000</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8662</t>
+          <t>https://portal.swarajability.org/apply-job/8544</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3196,19 +3188,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>• Arrange and organize products neatly on shelves and storage areas • Pick and pack items accurately for online orders • Assist in stock handling, replenishment, and inventory checks • Check product quality, expiry dates, and proper labelling • Maintain cleanliness in the work area</t>
+          <t>About the Role The Equity Dealer will be responsible for managing high-net-worth customers, activating accounts, and generating revenue through the trading of equities and related investment products. The role involves acquiring new clients, cross-selling various financial products, and building a p</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Brooke India Internship Program for PWD Candidates</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zudio - AP</t>
+          <t>Brooke Hospital For Animals (India)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -3217,7 +3209,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3235,28 +3227,20 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>INR 100000 - 150000 per year</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M40" t="n">
-        <v>150000</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8650</t>
+          <t>https://portal.swarajability.org/apply-job/8430</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3266,19 +3250,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Visual Merchandiser : Arranges products, displays, and signage to attract customers and promote sales</t>
+          <t>Roles &amp; Responsibilities Interns will work closely with Brooke Hospital for Animals (India) teams and contribute to ongoing programmes supporting working equines and the communities dependent on them. Based on the assigned department, responsibilities may include the following: 1. Funds &amp; Communicat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kitchen Staff</t>
+          <t>Trainee Apprentice</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bon Fresh Foods pvt ltd</t>
+          <t>RIL-AP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -3307,7 +3291,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 100000 - 300000 per year</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -3316,17 +3300,17 @@
         <v>100000</v>
       </c>
       <c r="M41" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8580</t>
+          <t>https://portal.swarajability.org/apply-job/7995</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3336,19 +3320,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>· Preparing quick meals like Magi, Poha, Bread Butter Jam etc. · Following Grooming Standards · Cleaning the tea making utensils · Mopping and cleaning the floor and ensuring the store is hygienically maintained · Cleaning tables and chairs · Reporting to duty on time as per the shift schedule · Mak</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analyst</t>
+          <t>Telecoller</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>FASTECH SERVICES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3377,26 +3361,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INR 800000 - 950000 per year</t>
+          <t>INR 50000 - 125000 per year</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="M42" t="n">
-        <v>950000</v>
+        <v>125000</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8566</t>
+          <t>https://portal.swarajability.org/apply-job/7282</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3406,19 +3390,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>About the Team The Credit Reporting team is responsible for Investment and Performance Reporting for Private Credit Funds . This role involves close collaboration with the Credit Reporting team in New York , supporting quarterly reporting, performance analytics, reconciliations, and client servicing</t>
+          <t>pakking</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Equity Dealer / Equity Dealer</t>
+          <t>CSE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Axis Securities Limited</t>
+          <t>TECHNOTASK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -3445,20 +3429,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>INR 100000 - 300000 per year</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>300000</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8544</t>
+          <t>https://portal.swarajability.org/apply-job/8006</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3468,19 +3460,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>About the Role The Equity Dealer will be responsible for managing high-net-worth customers, activating accounts, and generating revenue through the trading of equities and related investment products. The role involves acquiring new clients, cross-selling various financial products, and building a p</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brooke India Internship Program for PWD Candidates</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooke Hospital For Animals (India)</t>
+          <t>SVC HR Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -3489,7 +3481,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3507,20 +3499,28 @@
           <t>custom_api</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>INR 100000 - 300000 per year</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>300000</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8430</t>
+          <t>https://portal.swarajability.org/apply-job/7991</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3530,19 +3530,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Roles &amp; Responsibilities Interns will work closely with Brooke Hospital for Animals (India) teams and contribute to ongoing programmes supporting working equines and the communities dependent on them. Based on the assigned department, responsibilities may include the following: 1. Funds &amp; Communicat</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Trainee Apprentice</t>
+          <t>Senior Assistant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RIL-AP</t>
+          <t>Quess Corp Limited - Vijayawada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -3585,12 +3585,12 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7995</t>
+          <t>https://portal.swarajability.org/apply-job/7993</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3607,12 +3607,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Telecoller</t>
+          <t>Helper</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FASTECH SERVICES</t>
+          <t>Winley Polymers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -3641,26 +3641,26 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INR 50000 - 125000 per year</t>
+          <t>INR 100000 - 200000 per year</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="M46" t="n">
-        <v>125000</v>
+        <v>200000</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7282</t>
+          <t>https://portal.swarajability.org/apply-job/7128</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3670,19 +3670,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>pakking</t>
+          <t>Helper Job</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>SECURITY GAURD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TECHNOTASK</t>
+          <t>SAI SECURITY SERVICES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3711,26 +3711,26 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INR 100000 - 300000 per year</t>
+          <t>INR 150000 - 175000 per year</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="M47" t="n">
-        <v>300000</v>
+        <v>175000</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/8006</t>
+          <t>https://portal.swarajability.org/apply-job/7095</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3740,19 +3740,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Perform assigned duties efficiently and on time.</t>
+          <t>TO Maintain attendance records of company worker and goods in out registers and records.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Office Boy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SVC HR Solutions</t>
+          <t>Theurban clad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3781,26 +3781,26 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>INR 100000 - 300000 per year</t>
+          <t>INR 80000 - 90000 per year</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="M48" t="n">
-        <v>300000</v>
+        <v>90000</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7991</t>
+          <t>https://portal.swarajability.org/apply-job/7090</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3810,19 +3810,19 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Perform assigned duties efficiently and on time.</t>
+          <t>I Have Shervani &amp; Jotpuri Manufacturing Plant as Well as my office also that’s why i need a office boy</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Assistant</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quess Corp Limited - Vijayawada</t>
+          <t>Jagruthi HR Services</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>INR 100000 - 300000 per year</t>
+          <t>INR 100000 - 125000 per year</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3860,17 +3860,17 @@
         <v>100000</v>
       </c>
       <c r="M49" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7993</t>
+          <t>https://portal.swarajability.org/apply-job/7050</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -3880,19 +3880,19 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Perform assigned duties efficiently and on time.</t>
+          <t>Picker</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Helper</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Winley Polymers</t>
+          <t>Landmark Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>INR 100000 - 200000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -3930,17 +3930,17 @@
         <v>100000</v>
       </c>
       <c r="M50" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7128</t>
+          <t>https://portal.swarajability.org/apply-job/7049</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3950,19 +3950,19 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Helper Job</t>
+          <t>Retail Merchandise</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SECURITY GAURD</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAI SECURITY SERVICES</t>
+          <t>Big Basket</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3991,26 +3991,26 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>INR 150000 - 175000 per year</t>
+          <t>INR 100000 - 150000 per year</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M51" t="n">
         <v>150000</v>
-      </c>
-      <c r="M51" t="n">
-        <v>175000</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7095</t>
+          <t>https://portal.swarajability.org/apply-job/7047</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4020,19 +4020,19 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>TO Maintain attendance records of company worker and goods in out registers and records.</t>
+          <t>Associte</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Office Boy</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Theurban clad</t>
+          <t>Adhaan Solution</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -4061,26 +4061,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INR 80000 - 90000 per year</t>
+          <t>INR 100000 - 300000 per year</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="M52" t="n">
-        <v>90000</v>
+        <v>300000</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7090</t>
+          <t>https://portal.swarajability.org/apply-job/7704</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4090,19 +4090,19 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>I Have Shervani &amp; Jotpuri Manufacturing Plant as Well as my office also that’s why i need a office boy</t>
+          <t>Perform assigned duties efficiently and on time.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Liftman</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jagruthi HR Services</t>
+          <t>white house community</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -4131,26 +4131,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>INR 100000 - 125000 per year</t>
+          <t>INR 80000 - 100000 per year</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M53" t="n">
         <v>100000</v>
-      </c>
-      <c r="M53" t="n">
-        <v>125000</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7050</t>
+          <t>https://portal.swarajability.org/apply-job/6237</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -4160,19 +4160,19 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Picker</t>
+          <t>Safely operating the lift machinery, whether it's an elevator, forklift, or other type of lifting equipment, to transport passengers or materials between floors or locations. Assisting passengers in and out of the lift, ensuring their safety, and helping with loading and unloading materials as neede</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Office Boy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Landmark Group</t>
+          <t>Hera Agro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -4201,26 +4201,26 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 90000 - 100000 per year</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M54" t="n">
         <v>100000</v>
-      </c>
-      <c r="M54" t="n">
-        <v>150000</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7049</t>
+          <t>https://portal.swarajability.org/apply-job/6049</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -4230,19 +4230,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Retail Merchandise</t>
+          <t>Office Boy</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Big Basket</t>
+          <t>Ajay Farm House</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -4271,13 +4271,13 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>INR 100000 - 150000 per year</t>
+          <t>INR 80000 - 150000 per year</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="M55" t="n">
         <v>150000</v>
@@ -4285,12 +4285,12 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://portal.swarajability.org/job/7047</t>
+          <t>https://portal.swarajability.org/apply-job/5907</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4299,286 +4299,6 @@
         </is>
       </c>
       <c r="R55" t="inlineStr">
-        <is>
-          <t>Associte</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Adhaan Solution</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>explicit_pwd</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>custom_api</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>INR 100000 - 300000 per year</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M56" t="n">
-        <v>300000</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>https://portal.swarajability.org/job/7704</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>swarajability</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Perform assigned duties efficiently and on time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Liftman</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>white house community</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>explicit_pwd</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>custom_api</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>INR 80000 - 100000 per year</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>80000</v>
-      </c>
-      <c r="M57" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>https://portal.swarajability.org/job/6237</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>swarajability</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Safely operating the lift machinery, whether it's an elevator, forklift, or other type of lifting equipment, to transport passengers or materials between floors or locations. Assisting passengers in and out of the lift, ensuring their safety, and helping with loading and unloading materials as neede</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Office Boy</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Hera Agro</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>explicit_pwd</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>custom_api</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>INR 90000 - 100000 per year</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>90000</v>
-      </c>
-      <c r="M58" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>https://portal.swarajability.org/job/6049</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>swarajability</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Office Boy</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Ajay Farm House</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>explicit_pwd</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>custom_api</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>INR 80000 - 150000 per year</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>80000</v>
-      </c>
-      <c r="M59" t="n">
-        <v>150000</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>https://portal.swarajability.org/job/5907</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>swarajability</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
